--- a/StructureDefinition-FoodAllergy.xlsx
+++ b/StructureDefinition-FoodAllergy.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1291" uniqueCount="332">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-02-27T22:48:25+00:00</t>
+    <t>2022-02-27T22:59:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -651,13 +651,10 @@
 The 'substanceExposureRisk' extension is available as a structured and more flexible alternative to the 'code' element for making positive or negative allergy or intolerance statements.  This extension provides the capability to make "no known allergy" (or "no risk of adverse reaction") statements regarding any coded substance/product (including cases when a pre-coordinated "no allergy to x" concept for that substance/product does not exist).  If the 'substanceExposureRisk' extension is present, the AllergyIntolerance.code element SHALL be omitted.</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Type of the substance/product, allergy or intolerance condition, or negation/exclusion codes for reporting no known allergies.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/allergyintolerance-code</t>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>http://example.com/fhir/example/ValueSet/FoodAllergyVS</t>
   </si>
   <si>
     <t>substance/product:@@ -951,6 +948,9 @@
   </si>
   <si>
     <t>Coding of the specific substance (or pharmaceutical product) with a terminology capable of triggering decision support should be used wherever possible.  The 'code' element allows for the use of a specific substance or pharmaceutical product, or a group or class of substances. In the case of an allergy or intolerance to a class of substances, (for example, "penicillins"), the 'reaction.substance' element could be used to code the specific substance that was identified as having caused the reaction (for example, "amoxycillin"). Duplication of the value in the 'code' and 'reaction.substance' elements is acceptable when a specific substance has been recorded in 'code'.</t>
+  </si>
+  <si>
+    <t>example</t>
   </si>
   <si>
     <t>Codes defining the type of the substance (including pharmaceutical products).</t>
@@ -3226,11 +3226,9 @@
       <c r="W17" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="X17" t="s" s="2">
+      <c r="X17" s="2"/>
+      <c r="Y17" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="Z17" t="s" s="2">
         <v>78</v>
@@ -3263,22 +3261,22 @@
         <v>97</v>
       </c>
       <c r="AJ17" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AK17" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="AK17" t="s" s="2">
+      <c r="AL17" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>207</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" t="s" s="2">
@@ -3297,13 +3295,13 @@
         <v>86</v>
       </c>
       <c r="J18" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="K18" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="K18" t="s" s="2">
+      <c r="L18" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="L18" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
@@ -3354,7 +3352,7 @@
         <v>78</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AF18" t="s" s="2">
         <v>85</v>
@@ -3369,18 +3367,18 @@
         <v>97</v>
       </c>
       <c r="AJ18" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AK18" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="AK18" t="s" s="2">
+      <c r="AL18" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>215</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
@@ -3403,13 +3401,13 @@
         <v>78</v>
       </c>
       <c r="J19" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="K19" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="K19" t="s" s="2">
+      <c r="L19" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="L19" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
@@ -3460,7 +3458,7 @@
         <v>78</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AF19" t="s" s="2">
         <v>76</v>
@@ -3475,10 +3473,10 @@
         <v>97</v>
       </c>
       <c r="AJ19" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AK19" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="AK19" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>78</v>
@@ -3486,7 +3484,7 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
@@ -3509,13 +3507,13 @@
         <v>78</v>
       </c>
       <c r="J20" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="K20" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="K20" t="s" s="2">
+      <c r="L20" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="L20" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
@@ -3566,7 +3564,7 @@
         <v>78</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AF20" t="s" s="2">
         <v>76</v>
@@ -3581,10 +3579,10 @@
         <v>97</v>
       </c>
       <c r="AJ20" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AK20" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AK20" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>78</v>
@@ -3592,7 +3590,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
@@ -3615,13 +3613,13 @@
         <v>78</v>
       </c>
       <c r="J21" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="K21" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="K21" t="s" s="2">
+      <c r="L21" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="L21" t="s" s="2">
-        <v>231</v>
       </c>
       <c r="M21" s="2"/>
       <c r="N21" s="2"/>
@@ -3672,7 +3670,7 @@
         <v>78</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AF21" t="s" s="2">
         <v>76</v>
@@ -3687,22 +3685,22 @@
         <v>97</v>
       </c>
       <c r="AJ21" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AK21" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="AK21" t="s" s="2">
+      <c r="AL21" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>234</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" t="s" s="2">
@@ -3721,13 +3719,13 @@
         <v>78</v>
       </c>
       <c r="J22" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="K22" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="K22" t="s" s="2">
+      <c r="L22" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="L22" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
@@ -3778,7 +3776,7 @@
         <v>78</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AF22" t="s" s="2">
         <v>76</v>
@@ -3793,10 +3791,10 @@
         <v>97</v>
       </c>
       <c r="AJ22" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AK22" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="AK22" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>78</v>
@@ -3804,11 +3802,11 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" t="s" s="2">
@@ -3827,16 +3825,16 @@
         <v>86</v>
       </c>
       <c r="J23" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="K23" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="K23" t="s" s="2">
+      <c r="L23" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
@@ -3886,7 +3884,7 @@
         <v>78</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AF23" t="s" s="2">
         <v>76</v>
@@ -3901,18 +3899,18 @@
         <v>97</v>
       </c>
       <c r="AJ23" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AK23" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="AK23" t="s" s="2">
+      <c r="AL23" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>250</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
@@ -3935,16 +3933,16 @@
         <v>78</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
@@ -3994,7 +3992,7 @@
         <v>78</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AF24" t="s" s="2">
         <v>76</v>
@@ -4009,7 +4007,7 @@
         <v>97</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>78</v>
@@ -4020,7 +4018,7 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
@@ -4043,16 +4041,16 @@
         <v>78</v>
       </c>
       <c r="J25" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="K25" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="K25" t="s" s="2">
+      <c r="L25" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
@@ -4102,7 +4100,7 @@
         <v>78</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AF25" t="s" s="2">
         <v>76</v>
@@ -4117,7 +4115,7 @@
         <v>97</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>78</v>
@@ -4128,7 +4126,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
@@ -4151,13 +4149,13 @@
         <v>78</v>
       </c>
       <c r="J26" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="K26" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="K26" t="s" s="2">
+      <c r="L26" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
@@ -4208,7 +4206,7 @@
         <v>78</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AF26" t="s" s="2">
         <v>76</v>
@@ -4223,7 +4221,7 @@
         <v>97</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>78</v>
@@ -4234,7 +4232,7 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
@@ -4260,10 +4258,10 @@
         <v>87</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
@@ -4314,7 +4312,7 @@
         <v>78</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AF27" t="s" s="2">
         <v>76</v>
@@ -4329,7 +4327,7 @@
         <v>78</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>78</v>
@@ -4340,7 +4338,7 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
@@ -4366,10 +4364,10 @@
         <v>131</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="L28" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
@@ -4408,17 +4406,17 @@
         <v>78</v>
       </c>
       <c r="AA28" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AB28" s="2"/>
       <c r="AC28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD28" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AE28" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="AF28" t="s" s="2">
         <v>76</v>
@@ -4444,10 +4442,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C29" t="s" s="2">
         <v>78</v>
@@ -4469,16 +4467,16 @@
         <v>78</v>
       </c>
       <c r="J29" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="K29" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="K29" t="s" s="2">
+      <c r="L29" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
@@ -4528,7 +4526,7 @@
         <v>78</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AF29" t="s" s="2">
         <v>76</v>
@@ -4537,13 +4535,13 @@
         <v>77</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>136</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>78</v>
@@ -4554,11 +4552,11 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" t="s" s="2">
@@ -4580,10 +4578,10 @@
         <v>131</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="M30" t="s" s="2">
         <v>134</v>
@@ -4638,7 +4636,7 @@
         <v>78</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AF30" t="s" s="2">
         <v>76</v>
@@ -4664,7 +4662,7 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
@@ -4690,13 +4688,13 @@
         <v>152</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
@@ -4722,7 +4720,7 @@
         <v>78</v>
       </c>
       <c r="W31" t="s" s="2">
-        <v>202</v>
+        <v>293</v>
       </c>
       <c r="X31" t="s" s="2">
         <v>294</v>
@@ -4746,7 +4744,7 @@
         <v>78</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AF31" t="s" s="2">
         <v>76</v>
@@ -4830,7 +4828,7 @@
         <v>78</v>
       </c>
       <c r="W32" t="s" s="2">
-        <v>202</v>
+        <v>293</v>
       </c>
       <c r="X32" t="s" s="2">
         <v>302</v>
@@ -5011,7 +5009,7 @@
         <v>78</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K34" t="s" s="2">
         <v>312</v>
@@ -5083,7 +5081,7 @@
         <v>97</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>78</v>
@@ -5260,7 +5258,7 @@
         <v>78</v>
       </c>
       <c r="W36" t="s" s="2">
-        <v>202</v>
+        <v>293</v>
       </c>
       <c r="X36" t="s" s="2">
         <v>325</v>
@@ -5333,7 +5331,7 @@
         <v>78</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K37" t="s" s="2">
         <v>329</v>
@@ -5407,7 +5405,7 @@
         <v>97</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>78</v>

--- a/StructureDefinition-FoodAllergy.xlsx
+++ b/StructureDefinition-FoodAllergy.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-02-27T22:59:15+00:00</t>
+    <t>2022-02-27T23:28:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
